--- a/docs/source/tutorials/production_planning/materials/model/model_settings.xlsx
+++ b/docs/source/tutorials/production_planning/materials/model/model_settings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git_repos\pyesm\tests\models\integrated\1_coupled_model\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://polimi365.sharepoint.com/sites/DENG-SESAM/Documenti condivisi/c-Research/b-Models/CVXlab/tutorials/tutorial_website/model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28AFD02-90F5-444D-A928-4FCA652F2259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="124" documentId="13_ncr:1_{D28AFD02-90F5-444D-A928-4FCA652F2259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE3C0AE4-F0FF-419A-9703-F6A62A804C4E}"/>
   <bookViews>
-    <workbookView xWindow="-37640" yWindow="760" windowWidth="28800" windowHeight="15370" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="structure_sets" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="52">
   <si>
     <t>set_key</t>
   </si>
@@ -35,9 +35,6 @@
     <t>split_problem</t>
   </si>
   <si>
-    <t>copy_from</t>
-  </si>
-  <si>
     <t>table_key</t>
   </si>
   <si>
@@ -47,15 +44,9 @@
     <t>coordinates</t>
   </si>
   <si>
-    <t>value</t>
-  </si>
-  <si>
     <t>exogenous</t>
   </si>
   <si>
-    <t>problem_key</t>
-  </si>
-  <si>
     <t>objective</t>
   </si>
   <si>
@@ -68,125 +59,146 @@
     <t>filters</t>
   </si>
   <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>resources</t>
-  </si>
-  <si>
-    <t>environmental transactions</t>
-  </si>
-  <si>
-    <t>products</t>
-  </si>
-  <si>
-    <t>products of the system</t>
-  </si>
-  <si>
-    <t>product_data</t>
-  </si>
-  <si>
-    <t>ancillary data</t>
-  </si>
-  <si>
     <t>x</t>
   </si>
   <si>
     <t>products supply</t>
   </si>
   <si>
-    <t>resources, products</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>energy use</t>
+    <t>c</t>
+  </si>
+  <si>
+    <t>Maximize(c @ tran(x))</t>
+  </si>
+  <si>
+    <t>x &gt;= 0</t>
+  </si>
+  <si>
+    <t>variables_info</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>dim: cols</t>
+  </si>
+  <si>
+    <t>maximization of total profit</t>
+  </si>
+  <si>
+    <t>energy use less than endowment</t>
+  </si>
+  <si>
+    <t>positive products supply</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>Attributes</t>
+  </si>
+  <si>
+    <t>attributes of the products | dimension set</t>
+  </si>
+  <si>
+    <t>products | dimension set</t>
+  </si>
+  <si>
+    <t>scenarios for energy availability | inter-problem set</t>
+  </si>
+  <si>
+    <t>scenarios for material availability | inter-problem set</t>
+  </si>
+  <si>
+    <t>type: [profit, energy, material]</t>
+  </si>
+  <si>
+    <t>production</t>
+  </si>
+  <si>
+    <t>energy_avail</t>
+  </si>
+  <si>
+    <t>material_avail</t>
+  </si>
+  <si>
+    <t>attributes of products | energy use</t>
+  </si>
+  <si>
+    <t>attributes of products | material use</t>
+  </si>
+  <si>
+    <t>availability scenarios for energy</t>
+  </si>
+  <si>
+    <t>availability scenarios for material</t>
+  </si>
+  <si>
+    <t>endogenous</t>
+  </si>
+  <si>
+    <t>Scenarios_energy</t>
+  </si>
+  <si>
+    <t>Scenarios_material</t>
+  </si>
+  <si>
+    <t>Products, Scenarios_energy, Scenarios_material</t>
+  </si>
+  <si>
+    <t>Products, Attributes</t>
+  </si>
+  <si>
+    <t>e</t>
+  </si>
+  <si>
+    <t>m</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>attributes of products | profits</t>
+  </si>
+  <si>
+    <t>dim: rows, filters: {type: profit}</t>
+  </si>
+  <si>
+    <t>dim: rows, filters: {type: energy}</t>
+  </si>
+  <si>
+    <t>dim: rows, filters: {type: material}</t>
+  </si>
+  <si>
+    <t>e @ tran(x) - E &lt;= 0</t>
+  </si>
+  <si>
+    <t>m @ tran(x) - M &lt;= 0</t>
+  </si>
+  <si>
+    <t>material use less than endowment</t>
   </si>
   <si>
     <t>products_data</t>
-  </si>
-  <si>
-    <t>product data</t>
-  </si>
-  <si>
-    <t>products, product_data</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>a_0</t>
-  </si>
-  <si>
-    <t>lr</t>
-  </si>
-  <si>
-    <t>b</t>
-  </si>
-  <si>
-    <t>energy availability</t>
-  </si>
-  <si>
-    <t>Maximize(c @ tran(x))</t>
-  </si>
-  <si>
-    <t>a @ tran(x) - b &lt;= 0</t>
-  </si>
-  <si>
-    <t>x &gt;= 0</t>
-  </si>
-  <si>
-    <t>a - a_0 - lr @ diag(x) == 0</t>
-  </si>
-  <si>
-    <t>variables_info</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>1: endogenous, 2: exogenous</t>
-  </si>
-  <si>
-    <t>1: exogenous, 2: endogenous</t>
-  </si>
-  <si>
-    <t>dim: cols</t>
-  </si>
-  <si>
-    <t>dim: rows, filters: {category: [profit]}</t>
-  </si>
-  <si>
-    <t>dim: rows, filters: {category: [energy_use_0]}</t>
-  </si>
-  <si>
-    <t>dim: rows, filters: {category: [learning_rate]}</t>
-  </si>
-  <si>
-    <t>category: [energy_use_0, learning_rate, profit]</t>
-  </si>
-  <si>
-    <t>maximization of total profit</t>
-  </si>
-  <si>
-    <t>energy use less than endowment</t>
-  </si>
-  <si>
-    <t>positive products supply</t>
-  </si>
-  <si>
-    <t>energy use per unit of product</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -212,21 +224,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -240,13 +245,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF0EFEB1-6ECC-43D2-AB72-C998AF198F27}" name="Table1" displayName="Table1" ref="A1:E4" totalsRowShown="0">
-  <autoFilter ref="A1:E4" xr:uid="{BF0EFEB1-6ECC-43D2-AB72-C998AF198F27}"/>
-  <tableColumns count="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BF0EFEB1-6ECC-43D2-AB72-C998AF198F27}" name="Table1" displayName="Table1" ref="A1:D5" totalsRowShown="0">
+  <autoFilter ref="A1:D5" xr:uid="{BF0EFEB1-6ECC-43D2-AB72-C998AF198F27}"/>
+  <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{B25B1879-C5E9-4EB5-B028-F8512D272279}" name="set_key"/>
     <tableColumn id="9" xr3:uid="{DF8CC285-45E4-43D5-B8D8-803C745D6940}" name="description"/>
     <tableColumn id="4" xr3:uid="{A3D9FB3A-774D-46EA-8E98-EFD15E392CBD}" name="split_problem"/>
-    <tableColumn id="2" xr3:uid="{63BC0DE3-0E2B-46D5-92FB-25DE1E0A2CA9}" name="copy_from"/>
     <tableColumn id="8" xr3:uid="{AD5E32F7-2499-45CB-8B2A-F64E57F8E7E0}" name="filters"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -254,29 +258,25 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7FBD057B-B132-4379-814B-BD2BA1AFF594}" name="Table33" displayName="Table33" ref="A1:J7" totalsRowShown="0">
-  <autoFilter ref="A1:J7" xr:uid="{DB6E5FDC-ADDB-4F17-8178-C8D1F44ADCB4}"/>
-  <tableColumns count="10">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{7FBD057B-B132-4379-814B-BD2BA1AFF594}" name="Table33" displayName="Table33" ref="A1:G7" totalsRowShown="0">
+  <autoFilter ref="A1:G7" xr:uid="{DB6E5FDC-ADDB-4F17-8178-C8D1F44ADCB4}"/>
+  <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{3664E1C1-CDFB-4B96-B741-E3CF345A906A}" name="table_key"/>
     <tableColumn id="2" xr3:uid="{5DB24C0C-CFD3-4FB5-B53C-BFA40764E5FC}" name="description"/>
     <tableColumn id="3" xr3:uid="{2CD084FF-A0EF-4965-9069-628404776301}" name="type"/>
-    <tableColumn id="6" xr3:uid="{B7CAE23A-6C35-46F2-A86D-E8752E453E5D}" name="integer"/>
     <tableColumn id="4" xr3:uid="{727E494E-41A0-4D77-8D19-13F369E12AD0}" name="coordinates"/>
     <tableColumn id="5" xr3:uid="{5A4D7801-B865-4C40-AD87-418D7622F733}" name="variables_info"/>
-    <tableColumn id="10" xr3:uid="{CC0851B1-83C4-404D-8BB0-4F06479F0740}" name="value"/>
-    <tableColumn id="7" xr3:uid="{D8623746-1C30-46EA-97D5-95DE0D4F3D8A}" name="resources"/>
-    <tableColumn id="8" xr3:uid="{884F320F-DEF8-4E96-B1F4-579BB9297CB9}" name="products"/>
-    <tableColumn id="9" xr3:uid="{0DF16758-74BF-4847-8B66-F69C962A8892}" name="product_data"/>
+    <tableColumn id="8" xr3:uid="{884F320F-DEF8-4E96-B1F4-579BB9297CB9}" name="Products"/>
+    <tableColumn id="9" xr3:uid="{0DF16758-74BF-4847-8B66-F69C962A8892}" name="Attributes"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E7FEE58-959B-4A76-BD2C-C7A4A140E173}" name="Table4" displayName="Table4" ref="A1:D5" totalsRowShown="0">
-  <autoFilter ref="A1:D5" xr:uid="{9E7FEE58-959B-4A76-BD2C-C7A4A140E173}"/>
-  <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{339B6BC6-DC77-44F3-BC7D-5887B7C1C68A}" name="problem_key" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{9E7FEE58-959B-4A76-BD2C-C7A4A140E173}" name="Table4" displayName="Table4" ref="A1:C5" totalsRowShown="0">
+  <autoFilter ref="A1:C5" xr:uid="{9E7FEE58-959B-4A76-BD2C-C7A4A140E173}"/>
+  <tableColumns count="3">
     <tableColumn id="2" xr3:uid="{7D3A5DDD-E4D2-4BFD-8F61-20DAAF76C565}" name="objective"/>
     <tableColumn id="3" xr3:uid="{F83410DB-FD97-4F82-A158-44491E25E434}" name="expressions"/>
     <tableColumn id="4" xr3:uid="{9BA42D33-7C36-4CDA-8AAE-32BCE0C105B1}" name="description"/>
@@ -548,62 +548,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="33.81640625" customWidth="1"/>
-    <col min="3" max="4" width="15.08984375" customWidth="1"/>
-    <col min="5" max="5" width="51.6328125" customWidth="1"/>
-    <col min="6" max="7" width="10.54296875" customWidth="1"/>
+    <col min="1" max="1" width="19.81640625" customWidth="1"/>
+    <col min="2" max="2" width="45.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.26953125" customWidth="1"/>
+    <col min="5" max="5" width="29.54296875" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D2" s="2"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>45</v>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -617,177 +625,162 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F872E8C-C62E-4F3F-A20F-41906D0144C1}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.81640625" customWidth="1"/>
-    <col min="2" max="2" width="22.90625" customWidth="1"/>
-    <col min="3" max="3" width="28.26953125" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" customWidth="1"/>
-    <col min="7" max="7" width="8" customWidth="1"/>
-    <col min="8" max="8" width="13.54296875" customWidth="1"/>
-    <col min="9" max="9" width="19.81640625" customWidth="1"/>
-    <col min="10" max="10" width="40.90625" customWidth="1"/>
+    <col min="2" max="2" width="33.6328125" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="45.7265625" customWidth="1"/>
+    <col min="5" max="5" width="13.6328125" customWidth="1"/>
+    <col min="6" max="6" width="19.81640625" customWidth="1"/>
+    <col min="7" max="7" width="40.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>21</v>
+      </c>
+      <c r="G1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1" t="s">
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" t="s">
         <v>5</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D3" t="s">
+        <v>39</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>51</v>
+      </c>
+      <c r="B4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" t="s">
+        <v>39</v>
+      </c>
+      <c r="E4" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C7" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>20</v>
-      </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="E7" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>27</v>
-      </c>
-      <c r="F6" t="s">
-        <v>30</v>
-      </c>
-      <c r="I6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J6" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -800,77 +793,382 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB4DB9B-67B8-45E9-9CD6-D02B1BE46AE7}">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14" style="1" customWidth="1"/>
-    <col min="2" max="2" width="24.08984375" customWidth="1"/>
-    <col min="3" max="3" width="23.90625" customWidth="1"/>
-    <col min="4" max="4" width="30.81640625" customWidth="1"/>
+    <col min="1" max="1" width="24.08984375" customWidth="1"/>
+    <col min="2" max="2" width="23.90625" customWidth="1"/>
+    <col min="3" max="3" width="30.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="1">
-        <v>1</v>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>48</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="1">
-        <v>1</v>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="1">
-        <v>2</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D5" t="s">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="e67e9a88-35e1-4b39-8da9-a609eb308282" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100241E96938535DD4B921FCDFB54345D30" ma:contentTypeVersion="19" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="7b5477e5183001dfb744417d6d3e1bdb">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e" xmlns:ns3="e67e9a88-35e1-4b39-8da9-a609eb308282" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47c71bcc7ce4561c40563d7718896ae0" ns2:_="" ns3:_="">
+    <xsd:import namespace="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <xsd:import namespace="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="16" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Tag immagine" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="62691f12-1220-44b1-ba48-e77f64da2991" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="25" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="26" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="e67e9a88-35e1-4b39-8da9-a609eb308282" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Condiviso con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Condiviso con dettagli" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cfe7f1f2-b186-4eae-b9db-3e53485d6587}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="e67e9a88-35e1-4b39-8da9-a609eb308282">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo di contenuto"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Titolo"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AACC1C13-A103-430F-9C87-7B7555F339C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8036AEDF-477D-4EE5-8FF9-44DD1F8D97B7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="5d44ae6a-e145-4c9d-94e7-ddf9cc58067e"/>
+    <ds:schemaRef ds:uri="e67e9a88-35e1-4b39-8da9-a609eb308282"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF6C7914-669F-419D-AE68-4CBD204B5F63}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>